--- a/Statistics/200m Medley_statistics.xlsx
+++ b/Statistics/200m Medley_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,12 +677,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christian Tronvoll</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.14,69</t>
+          <t>2.14,67</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -690,12 +690,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18.01.2014</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -712,12 +712,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Christian Tronvoll</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.14,67</t>
+          <t>2.14,69</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -725,12 +725,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>18.01.2014</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brage Wetjen Sigernes</t>
+          <t>Espen Singstad</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.19,42</t>
+          <t>2.19,38</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>17.09.2006</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1062,12 +1062,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Espen Singstad</t>
+          <t>Brage Wetjen Sigernes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.19,38</t>
+          <t>2.19,42</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17.09.2006</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1762,25 +1762,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.27,31</t>
+          <t>2.25,94</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>07.04.2013</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fauske</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1797,25 +1797,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Arnt Martin Ystenes</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.27,55</t>
+          <t>2.27,31</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.01.2010</t>
+          <t>07.04.2013</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fauske</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ådne Viken Refseth</t>
+          <t>Arnt Martin Ystenes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.27,48</t>
+          <t>2.27,55</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>22.01.2010</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1867,20 +1867,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Ådne Viken Refseth</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.27,96</t>
+          <t>2.27,48</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>03.12.2017</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1937,25 +1937,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.45,10</t>
+          <t>2.27,96</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19.01.2019</t>
+          <t>03.12.2017</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1972,20 +1972,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.28,62</t>
+          <t>2.45,10</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>19.01.2019</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2007,25 +2007,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brage Flem Habberstad</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.29,50</t>
+          <t>2.28,62</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>24.11.2012</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2042,25 +2042,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kjersti Arefjord</t>
+          <t>Brage Flem Habberstad</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.46,43</t>
+          <t>2.29,50</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>09.03.2019</t>
+          <t>24.11.2012</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2077,25 +2077,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Olav Nygård Bergum</t>
+          <t>Kjersti Arefjord</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.29,85</t>
+          <t>2.46,43</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>09.03.2019</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Elias Hauge Lien</t>
+          <t>Thais Farias Kristiansen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.31,00</t>
+          <t>2.47,94</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2252,12 +2252,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Thais Farias Kristiansen</t>
+          <t>Elias Hauge Lien</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.47,94</t>
+          <t>2.31,00</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2287,25 +2287,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Birk Skaalvik Trelstad</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.31,38</t>
+          <t>2.30,07</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>27.01.2024</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2322,20 +2322,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Leo Petter Hauge Sølvberg</t>
+          <t>Birk Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2.31,58</t>
+          <t>2.31,38</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14.01.2017</t>
+          <t>27.01.2024</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2357,20 +2357,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Leo Petter Hauge Sølvberg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.32,00</t>
+          <t>2.31,58</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>14.01.2017</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2532,25 +2532,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ask Yifei Baldersheim</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.35,75</t>
+          <t>2.33,69</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2567,25 +2567,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Simon Perssønn Mørseth</t>
+          <t>Ask Yifei Baldersheim</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.36,20</t>
+          <t>2.35,75</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>14.09.2024</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2637,25 +2637,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Simon Perssønn Mørseth</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.37,05</t>
+          <t>2.36,20</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>14.09.2024</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2672,25 +2672,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Even Kristoffer Lind Bøckman</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2.37,35</t>
+          <t>2.35,96</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2707,25 +2707,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2.37,33</t>
+          <t>2.37,05</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2742,20 +2742,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2.37,43</t>
+          <t>2.36,08</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10.02.2013</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2777,25 +2777,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Oliver Grøtte Ramstad</t>
+          <t>Even Kristoffer Lind Bøckman</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.37,57</t>
+          <t>2.37,35</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2812,25 +2812,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.38,14</t>
+          <t>2.37,43</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>10.02.2013</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2847,25 +2847,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vishnu Sattanathan</t>
+          <t>Oliver Grøtte Ramstad</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.38,56</t>
+          <t>2.37,57</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2882,25 +2882,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.38,78</t>
+          <t>2.38,14</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2917,25 +2917,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Vishnu Sattanathan</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.39,78</t>
+          <t>2.38,56</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2952,25 +2952,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bjørnar Bakkejord</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.40,69</t>
+          <t>2.39,78</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2987,20 +2987,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mattias Isaksen</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.40,89</t>
+          <t>2.39,26</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3022,25 +3022,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Bjørnar Bakkejord</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.41,85</t>
+          <t>2.40,69</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3057,25 +3057,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.42,38</t>
+          <t>2.40,89</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30.09.2018</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3092,12 +3092,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2.42,40</t>
+          <t>2.42,38</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>30.09.2018</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3127,25 +3127,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kristin Myhr Pettersen</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3.00,78</t>
+          <t>2.42,40</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3162,25 +3162,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Stian Nilsen</t>
+          <t>Kristin Myhr Pettersen</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2.43,89</t>
+          <t>3.00,78</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14.02.2010</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3197,25 +3197,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Stian Nilsen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.44,20</t>
+          <t>2.43,89</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26.05.2024</t>
+          <t>14.02.2010</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3337,25 +3337,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lionel Nicolas Weissbrodt</t>
+          <t>Lev Shestov</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.45,05</t>
+          <t>2.43,70</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01.10.2023</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3372,20 +3372,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Lionel Nicolas Weissbrodt</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2.45,18</t>
+          <t>2.45,05</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>29.10.2011</t>
+          <t>01.10.2023</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3407,25 +3407,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Erlend Skogland</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2.45,28</t>
+          <t>2.45,18</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04.12.2010</t>
+          <t>29.10.2011</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3442,25 +3442,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Erlend Skogland</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2.45,44</t>
+          <t>2.45,28</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>15.09.2018</t>
+          <t>04.12.2010</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3477,25 +3477,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Iris Elise Moen</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3.04,81</t>
+          <t>2.45,44</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30.09.2019</t>
+          <t>15.09.2018</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3512,25 +3512,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Carl Victor Mukisa Nygård</t>
+          <t>Iris Elise Moen</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.46,89</t>
+          <t>3.04,81</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>21.10.2022</t>
+          <t>30.09.2019</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3547,25 +3547,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>David Fjeld</t>
+          <t>Carl Victor Mukisa Nygård</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.47,22</t>
+          <t>2.46,89</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20.10.2007</t>
+          <t>21.10.2022</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3582,25 +3582,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Reidar Lorentzen</t>
+          <t>David Fjeld</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2.47,47</t>
+          <t>2.47,22</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>09.03.2012</t>
+          <t>20.10.2007</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3617,25 +3617,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Reidar Lorentzen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2.47,84</t>
+          <t>2.47,47</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>05.10.2014</t>
+          <t>09.03.2012</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Vegard S. Wigum</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>09.06.2025</t>
+          <t>05.10.2014</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3687,25 +3687,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Anton Sergeevich Gorodkov</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2.48,40</t>
+          <t>2.47,84</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3722,25 +3722,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Magnus Svindland Næsgaard</t>
+          <t>Anton Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2.48,64</t>
+          <t>2.48,40</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3757,20 +3757,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Johan Mostervik</t>
+          <t>Magnus Svindland Næsgaard</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2.49,51</t>
+          <t>2.48,64</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>12.11.2023</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3792,20 +3792,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Johan Mostervik</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2.49,81</t>
+          <t>2.49,51</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3827,25 +3827,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2.50,26</t>
+          <t>2.48,48</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3862,25 +3862,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Finn Øivind Fevang</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.50,30</t>
+          <t>2.48,47</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3897,20 +3897,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2.50,32</t>
+          <t>2.49,81</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>02.11.2013</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3932,20 +3932,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2.50,58</t>
+          <t>2.50,32</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>25.05.2008</t>
+          <t>12.11.2023</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3967,20 +3967,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Finn Øivind Fevang</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2.50,54</t>
+          <t>2.50,30</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20.03.2010</t>
+          <t>25.05.2008</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4037,12 +4037,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2.50,56</t>
+          <t>2.50,54</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>30.09.2019</t>
+          <t>19.06.2021</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4072,25 +4072,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kristian Myhr Høgstøl</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2.51,64</t>
+          <t>2.50,56</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>30.09.2019</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4107,25 +4107,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2.51,56</t>
+          <t>2.50,58</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>09.02.2014</t>
+          <t>20.03.2010</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4142,20 +4142,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Leander Gisvold Restad</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2.52,34</t>
+          <t>2.50,06</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4177,25 +4177,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Håkon Johansen</t>
+          <t>Kristian Myhr Høgstøl</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2.52,37</t>
+          <t>2.51,64</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4212,25 +4212,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Dhanushi Attanapola</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.12,78</t>
+          <t>2.51,56</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>24.05.2009</t>
+          <t>09.02.2014</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4247,25 +4247,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2.53,88</t>
+          <t>3.11,10</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4282,25 +4282,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bjørn Pedersen</t>
+          <t>Håkon Johansen</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2.54,08</t>
+          <t>2.52,37</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>12.03.2010</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4317,25 +4317,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ellen Kristine Eidsmo Hova</t>
+          <t>Leander Gisvold Restad</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.13,95</t>
+          <t>2.52,34</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4352,25 +4352,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2.54,57</t>
+          <t>3.12,34</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4387,25 +4387,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Dhanushi Attanapola</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2.54,56</t>
+          <t>3.12,78</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>24.05.2009</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4422,25 +4422,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>Bjørn Pedersen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2.56,11</t>
+          <t>2.54,08</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>12.03.2010</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4457,20 +4457,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Lyder Ringsvold Hogstad</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2.55,95</t>
+          <t>2.54,56</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4492,25 +4492,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ivan Erikovitch Alvestad</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2.56,21</t>
+          <t>2.54,33</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4527,25 +4527,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sondre Aakerholm Adsen</t>
+          <t>Lyder Ringsvold Hogstad</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2.56,84</t>
+          <t>2.55,95</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>21.10.2023</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4562,25 +4562,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2.56,89</t>
+          <t>2.56,11</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4597,20 +4597,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Ivan Erikovitch Alvestad</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2.57,04</t>
+          <t>2.56,21</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>09.02.2014</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4632,25 +4632,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ingjerd Jepsen Vegge</t>
+          <t>Sondre Aakerholm Adsen</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3.19,59</t>
+          <t>2.56,84</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>13.02.2011</t>
+          <t>21.10.2023</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4667,16 +4667,16 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.00,17</t>
+          <t>2.56,89</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4702,25 +4702,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3.20,87</t>
+          <t>2.57,04</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>09.02.2014</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4737,25 +4737,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Brage Gylseth Dahl</t>
+          <t>Liv Løfaldli</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.01,21</t>
+          <t>3.16,47</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4772,25 +4772,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3.01,64</t>
+          <t>3.18,19</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12.03.2010</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4807,25 +4807,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tamer Saleh Abuzid</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.03,02</t>
+          <t>3.18,30</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4842,20 +4842,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ailin Østerås</t>
+          <t>Ingjerd Jepsen Vegge</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.24,15</t>
+          <t>3.19,59</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>13.02.2011</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4877,25 +4877,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Brage Gylseth Dahl</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.04,12</t>
+          <t>3.01,21</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4912,25 +4912,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Victor Voormolen Gutierrez</t>
+          <t>Paal Aagaard</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.04,21</t>
+          <t>3.01,64</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>12.03.2010</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4947,25 +4947,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Oscar Kvaløy Tiller</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3.07,07</t>
+          <t>3.01,68</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>24.10.2021</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4982,25 +4982,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jon Noé Høye</t>
+          <t>Tamer Saleh Abuzid</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.07,16</t>
+          <t>3.03,02</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5017,20 +5017,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Conrad Sippala Hassel</t>
+          <t>Ailin Østerås</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3.07,77</t>
+          <t>3.24,15</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5052,25 +5052,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.30,17</t>
+          <t>3.02,36</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5087,25 +5087,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Liv Løfaldli</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3.30,53</t>
+          <t>3.04,12</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5122,16 +5122,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Emily Liv Liem</t>
+          <t>Victor Voormolen Gutierrez</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.32,57</t>
+          <t>3.04,21</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -5157,25 +5157,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Kaan Baltaci</t>
+          <t>Oscar Kvaløy Tiller</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3.13,18</t>
+          <t>3.07,07</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>14.01.2023</t>
+          <t>24.10.2021</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5192,25 +5192,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>William Wale</t>
+          <t>Jon Noé Høye</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3.14,03</t>
+          <t>3.07,16</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>05.10.2014</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5227,20 +5227,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>William Johannes Kirkelund Kristiansen</t>
+          <t>Conrad Sippala Hassel</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3.14,25</t>
+          <t>3.07,77</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14.01.2023</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5262,25 +5262,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Thomas Paulsen</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3.14,24</t>
+          <t>3.30,17</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>09.02.2014</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5297,25 +5297,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Emily Liv Liem</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.16,08</t>
+          <t>3.32,57</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5332,20 +5332,20 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Kaan Baltaci</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3.17,03</t>
+          <t>3.13,18</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>14.01.2023</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5367,20 +5367,20 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Bjørn Marius Hegge</t>
+          <t>William Wale</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.18,23</t>
+          <t>3.14,03</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>19.11.2022</t>
+          <t>05.10.2014</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5402,25 +5402,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>Thomas Paulsen</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3.21,90</t>
+          <t>3.14,24</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>09.02.2014</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5437,20 +5437,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>William Johannes Kirkelund Kristiansen</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.45,15</t>
+          <t>3.14,25</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>14.01.2023</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5472,25 +5472,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Setareh Kulsum Sigrid Feyzi</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3.45,71</t>
+          <t>3.13,99</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>30.09.2018</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5507,20 +5507,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Tor Martin Dahl</t>
+          <t>Bjørn Marius Hegge</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.23,58</t>
+          <t>3.18,23</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>19.11.2022</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5542,25 +5542,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Olav Høyland Hofstad</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3.24,51</t>
+          <t>3.21,90</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>03.12.2011</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5577,25 +5577,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Liem Emily Liv</t>
+          <t>Setareh Kulsum Sigrid Feyzi</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3.47,84</t>
+          <t>3.45,71</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>30.09.2018</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5612,20 +5612,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Peder Lund Juul</t>
+          <t>Tor Martin Dahl</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3.25,25</t>
+          <t>3.23,58</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5647,25 +5647,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Anton Hoel</t>
+          <t>Tymofii Dzisiak</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3.25,54</t>
+          <t>3.22,38</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>15.06.2013</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5682,25 +5682,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3.29,62</t>
+          <t>3.24,51</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5717,20 +5717,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sondre Thorgaard</t>
+          <t>Liem Emily Liv</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3.29,68</t>
+          <t>3.47,84</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>03.10.2021</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5752,20 +5752,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Marit Søberg</t>
+          <t>Peder Lund Juul</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3.54,56</t>
+          <t>3.25,25</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>11.10.2009</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5787,25 +5787,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Tymofii Dzisiak</t>
+          <t>Anton Hoel</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3.30,67</t>
+          <t>3.25,54</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>15.06.2013</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5822,25 +5822,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Jakob M. Tjøstheim</t>
+          <t>Bernard Smuk</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3.33,12</t>
+          <t>3.25,32</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5857,25 +5857,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Robin von Bargen</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3.33,15</t>
+          <t>3.27,41</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5892,20 +5892,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Anniken Skjøstad</t>
+          <t>Sondre Thorgaard</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3.56,86</t>
+          <t>3.29,68</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>03.10.2021</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5927,25 +5927,25 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Bernard Smuk</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3.34,75</t>
+          <t>3.28,35</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5962,25 +5962,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Marit Søberg</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3.35,68</t>
+          <t>3.54,56</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>11.10.2009</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5997,20 +5997,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Brage Kaminka Heiberg</t>
+          <t>Robin von Bargen</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>3.35,64</t>
+          <t>3.33,15</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>25.01.2009</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6032,25 +6032,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Jakob M. Tjøstheim</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4.02,52</t>
+          <t>3.33,12</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>02.11.2013</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6067,20 +6067,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Leo Alexander Farias Kristiansen</t>
+          <t>Anniken Skjøstad</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3.38,22</t>
+          <t>3.56,86</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6102,25 +6102,25 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ingvar Høgås Wik</t>
+          <t>Brage Kaminka Heiberg</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3.40,87</t>
+          <t>3.35,64</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>14.03.2015</t>
+          <t>12.11.2023</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6137,20 +6137,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Angelico Mikkel Andersen</t>
+          <t>Leo Alexander Farias Kristiansen</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3.42,26</t>
+          <t>3.38,22</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6172,25 +6172,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Magnus Hestvik Larsen</t>
+          <t>Ingvar Høgås Wik</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3.43,11</t>
+          <t>3.40,87</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>19.04.2009</t>
+          <t>14.03.2015</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6207,20 +6207,20 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>Angelico Mikkel Andersen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3.43,59</t>
+          <t>3.42,26</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6242,25 +6242,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Cornelius Wik</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3.45,09</t>
+          <t>4.07,83</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6277,25 +6277,25 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Vår Kristine Sollien Skar</t>
+          <t>Magnus Hestvik Larsen</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4.10,89</t>
+          <t>3.43,11</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>18.01.2014</t>
+          <t>19.04.2009</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6312,20 +6312,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Morten Johansen</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3.46,81</t>
+          <t>3.45,09</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>15.01.2006</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6347,25 +6347,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Kasper Steen Jensen</t>
+          <t>Vår Kristine Sollien Skar</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>3.49,94</t>
+          <t>4.10,89</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>18.01.2014</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6382,25 +6382,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Idun Skjærseth</t>
+          <t>Morten Johansen</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>4.20,98</t>
+          <t>3.46,81</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>15.01.2006</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6417,25 +6417,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Filip Dalsaune</t>
+          <t>Kasper Steen Jensen</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>3.57,01</t>
+          <t>3.49,94</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>02.11.2024</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6452,25 +6452,25 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Arild Håkonsen Stixrud</t>
+          <t>Idun Skjærseth</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3.58,34</t>
+          <t>4.20,98</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>03.12.2011</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6487,20 +6487,20 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Jesper Øvermo Johansen</t>
+          <t>Filip Dalsaune</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>4.00,79</t>
+          <t>3.57,01</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6522,20 +6522,20 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mikkel Fenstad</t>
+          <t>Arild Håkonsen Stixrud</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>4.04,26</t>
+          <t>3.58,34</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>12.11.2023</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6557,25 +6557,25 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sigurd Kristoffersen Torvik</t>
+          <t>Jesper Øvermo Johansen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>4.04,03</t>
+          <t>4.00,79</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6592,20 +6592,20 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Nikan Ommani</t>
+          <t>Mikkel Fenstad</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4.05,53</t>
+          <t>4.04,26</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6627,25 +6627,25 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Einar Risholt Moen</t>
+          <t>Sigurd Kristoffersen Torvik</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>4.06,99</t>
+          <t>4.04,03</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6662,20 +6662,20 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Randi Leiknes</t>
+          <t>Nikan Ommani</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>4.35,41</t>
+          <t>4.05,53</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>21.06.2008</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6697,20 +6697,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Marcus Thalberg Fagerheim</t>
+          <t>Einar Risholt Moen</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>4.07,81</t>
+          <t>4.06,99</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>10.10.2010</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6732,20 +6732,20 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Elias Lien</t>
+          <t>Randi Leiknes</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>4.13,28</t>
+          <t>4.35,41</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>15.09.2018</t>
+          <t>21.06.2008</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6767,20 +6767,20 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Dominic Olav Sollien-Pearn</t>
+          <t>Marcus Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>4.18,30</t>
+          <t>4.07,81</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>10.10.2010</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6802,25 +6802,25 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Fredrik Hårsaker Myrenget</t>
+          <t>Elias Lien</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>4.22,37</t>
+          <t>4.13,28</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>15.09.2018</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6837,25 +6837,25 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Hauk Vold Kirkvold</t>
+          <t>Guy Løfaldli</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>4.24,12</t>
+          <t>4.14,91</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6872,25 +6872,25 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Eirik Solligård</t>
+          <t>Dominic Olav Sollien-Pearn</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>4.26,60</t>
+          <t>4.18,30</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>14.02.2009</t>
+          <t>19.06.2021</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6907,25 +6907,25 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Hans Otto Søyseth</t>
+          <t>Fredrik Hårsaker Myrenget</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>4.41,06</t>
+          <t>4.22,37</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>14.03.2015</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6942,20 +6942,20 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Gajithsing Ajeethsing</t>
+          <t>Hauk Vold Kirkvold</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>4.45,25</t>
+          <t>4.24,12</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>17.04.2021</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6977,25 +6977,25 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Theodor Hoff</t>
+          <t>Eirik Solligård</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>4.45,10</t>
+          <t>4.26,60</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20.04.2013</t>
+          <t>14.02.2009</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7012,33 +7012,138 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
+          <t>Hans Otto Søyseth</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>4.41,06</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>59</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>14.03.2015</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Levanger</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Gajithsing Ajeethsing</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4.45,25</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>56</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>19.06.2021</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Theodor Hoff</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4.45,10</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>56</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>20.04.2013</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>Casper Dahle-Øfsti</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>4.47,36</t>
         </is>
       </c>
-      <c r="C189" t="n">
+      <c r="C192" t="n">
         <v>55</v>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>10.02.2013</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>Trondheim</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -7203,12 +7308,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Tudor Ignat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.18,49</t>
+          <t>2.18,54</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -7216,12 +7321,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.05.2021</t>
+          <t>08.08.2023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Funchal</t>
+          <t>Kyushu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7238,12 +7343,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tudor Ignat</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.18,54</t>
+          <t>2.18,49</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -7251,12 +7356,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08.08.2023</t>
+          <t>22.05.2021</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kyushu</t>
+          <t>Funchal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -8638,12 +8743,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.46,33</t>
+          <t>2.46,44</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -8673,12 +8778,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.46,44</t>
+          <t>2.46,33</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -8813,12 +8918,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oliver Grøtte Ramstad</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.48,99</t>
+          <t>2.49,13</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -8826,12 +8931,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>29.06.2024</t>
+          <t>14.04.2018</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -8848,12 +8953,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Oliver Grøtte Ramstad</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.49,13</t>
+          <t>2.48,99</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -8861,12 +8966,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14.04.2018</t>
+          <t>29.06.2024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9128,12 +9233,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2.55,85</t>
+          <t>2.55,93</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -9141,12 +9246,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>28.06.2025</t>
+          <t>13.04.2013</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -9163,12 +9268,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.55,93</t>
+          <t>2.55,85</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -9176,12 +9281,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>28.06.2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -10221,7 +10326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10719,12 +10824,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Julie Mathilde Bjordal</t>
+          <t>Maud Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.34,89</t>
+          <t>2.34,96</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -10732,12 +10837,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14.01.2017</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -10754,12 +10859,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maud Steinsdotter Nestgaard</t>
+          <t>Julie Mathilde Bjordal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.34,96</t>
+          <t>2.34,89</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -10767,12 +10872,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>14.01.2017</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10859,25 +10964,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rebekka Wangberg</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.35,64</t>
+          <t>2.35,18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10894,25 +10999,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Silje Pettersen Olden</t>
+          <t>Rebekka Wangberg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.36,84</t>
+          <t>2.35,64</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10929,20 +11034,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Elisabeth Wilmann</t>
+          <t>Silje Pettersen Olden</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.36,92</t>
+          <t>2.36,84</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10964,25 +11069,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Anne Bostad Hegvold</t>
+          <t>Elisabeth Wilmann</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.37,38</t>
+          <t>2.36,92</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12.03.2010</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -10999,25 +11104,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gudrun Berg Ildstad</t>
+          <t>Anne Bostad Hegvold</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.37,48</t>
+          <t>2.37,38</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>01.10.2011</t>
+          <t>12.03.2010</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -11034,25 +11139,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Gudrun Berg Ildstad</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.37,59</t>
+          <t>2.37,48</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18.10.2009</t>
+          <t>01.10.2011</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -11069,25 +11174,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karoline Borg Simonsen</t>
+          <t>Irja Gravdahl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.38,18</t>
+          <t>2.37,59</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>18.10.2009</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -11139,25 +11244,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Karoline Borg Simonsen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.38,76</t>
+          <t>2.38,18</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -11174,25 +11279,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Viktoria Juel</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.39,00</t>
+          <t>2.37,92</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13.02.2011</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -11209,25 +11314,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Edle Lund</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.39,14</t>
+          <t>2.38,76</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -11244,25 +11349,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vincente Quiles Saez</t>
+          <t>Viktoria Juel</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2.23,73</t>
+          <t>2.39,00</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20.03.2010</t>
+          <t>13.02.2011</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -11279,20 +11384,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Maja Graczyk</t>
+          <t>Edle Lund</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.40,99</t>
+          <t>2.39,14</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11314,25 +11419,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Carina Aadahl</t>
+          <t>Vincente Quiles Saez</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.41,00</t>
+          <t>2.23,73</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>20.03.2010</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11349,20 +11454,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ylva S. Dyngeland</t>
+          <t>Maja Graczyk</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.41,31</t>
+          <t>2.40,99</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>05.10.2014</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11384,25 +11489,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nora Yian Baldersheim</t>
+          <t>Carina Aadahl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.41,47</t>
+          <t>2.41,00</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11419,25 +11524,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Eirill Straum</t>
+          <t>Ylva S. Dyngeland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.42,23</t>
+          <t>2.41,31</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>05.10.2014</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11454,25 +11559,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Nora Yian Baldersheim</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.42,55</t>
+          <t>2.41,47</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11489,25 +11594,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Silje Aadahl</t>
+          <t>Eirill Straum</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.42,67</t>
+          <t>2.42,23</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>28.10.2017</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11524,25 +11629,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nina Alicja Skarø</t>
+          <t>Silje Aadahl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.43,19</t>
+          <t>2.42,67</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21.10.2017</t>
+          <t>28.10.2017</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11559,25 +11664,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Helle Krogstad</t>
+          <t>Nina Alicja Skarø</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.43,25</t>
+          <t>2.43,19</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10.02.2008</t>
+          <t>21.10.2017</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11594,25 +11699,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ingrid Elverum</t>
+          <t>Helle Krogstad</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.43,41</t>
+          <t>2.43,25</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>09.02.2014</t>
+          <t>10.02.2008</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11629,25 +11734,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hege Solberg Jørgensen</t>
+          <t>Ingrid Elverum</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.43,70</t>
+          <t>2.43,41</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>09.02.2014</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -11664,25 +11769,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Hege Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.44,01</t>
+          <t>2.43,70</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -11699,25 +11804,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.44,20</t>
+          <t>2.44,01</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>09.05.2010</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11734,25 +11839,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Julie Hegvik</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.44,43</t>
+          <t>2.44,20</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>18.10.2008</t>
+          <t>09.05.2010</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -11769,12 +11874,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Julie Hegvik</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.44,31</t>
+          <t>2.44,43</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -11782,12 +11887,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.02.2013</t>
+          <t>18.10.2008</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -11804,25 +11909,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solveig Natvig Løvseth</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.44,44</t>
+          <t>2.44,31</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>10.02.2013</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -11839,25 +11944,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mila Maria Flåan</t>
+          <t>Solveig Natvig Løvseth</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.45,28</t>
+          <t>2.44,44</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26.05.2024</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -11874,25 +11979,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Mila Maria Flåan</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.45,78</t>
+          <t>2.45,28</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>26.05.2024</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12049,12 +12154,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sigrid Eldholm</t>
+          <t>Thea Haugan</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.47,17</t>
+          <t>2.47,20</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -12062,12 +12167,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12084,12 +12189,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Thea Haugan</t>
+          <t>Sigrid Eldholm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.47,20</t>
+          <t>2.47,17</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -12097,12 +12202,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12259,25 +12364,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lisa Ling Klauseth Liasjø</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.48,00</t>
+          <t>2.47,51</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>08.02.2020</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -12294,25 +12399,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cesilie Solberg Jørgensen</t>
+          <t>Lisa Ling Klauseth Liasjø</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2.48,41</t>
+          <t>2.48,00</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>12.01.2013</t>
+          <t>08.02.2020</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12329,12 +12434,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Embla Mimi Baarholm</t>
+          <t>Tage Singstad</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.48,41</t>
+          <t>2.31,51</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -12342,12 +12447,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>10.04.2011</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12364,12 +12469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tage Singstad</t>
+          <t>Cesilie Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.31,51</t>
+          <t>2.48,41</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -12377,12 +12482,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.04.2011</t>
+          <t>12.01.2013</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12399,20 +12504,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Embla Mimi Baarholm</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.48,65</t>
+          <t>2.48,41</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17.09.2006</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -12434,20 +12539,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Vilde Austmo</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.49,44</t>
+          <t>2.48,65</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>17.09.2006</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -12469,25 +12574,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Vilde Austmo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2.49,80</t>
+          <t>2.49,44</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11.05.2013</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12504,25 +12609,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Torborg Duesten Blokkum</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2.50,01</t>
+          <t>2.49,80</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>28.03.2014</t>
+          <t>11.05.2013</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12539,25 +12644,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Torborg Duesten Blokkum</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2.50,33</t>
+          <t>2.50,01</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>28.03.2014</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12574,25 +12679,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.50,49</t>
+          <t>2.50,33</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12609,25 +12714,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ingrid Johansen</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.51,20</t>
+          <t>2.50,49</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20.10.2007</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12644,20 +12749,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.51,37</t>
+          <t>2.32,87</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -12679,25 +12784,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Ingrid Johansen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.34,79</t>
+          <t>2.51,20</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>20.10.2007</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -12714,20 +12819,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Linn Amalie Aresvik</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.52,16</t>
+          <t>2.51,37</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -12749,25 +12854,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Linn Amalie Aresvik</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.52,28</t>
+          <t>2.52,16</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>24.11.2012</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -12784,25 +12889,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.52,70</t>
+          <t>2.52,28</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>01.10.2023</t>
+          <t>24.11.2012</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -12819,25 +12924,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.52,84</t>
+          <t>2.52,70</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>01.10.2023</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -12889,20 +12994,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2.53,02</t>
+          <t>2.52,84</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12924,25 +13029,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Diana Stafsnes Califano</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2.53,47</t>
+          <t>2.53,02</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20.10.2019</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -12959,25 +13064,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Diana Stafsnes Califano</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2.53,59</t>
+          <t>2.53,47</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>20.10.2019</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -12994,25 +13099,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Monica Wold Gustafson</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.54,30</t>
+          <t>2.53,59</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -13029,20 +13134,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ane Viken Refseth</t>
+          <t>Monica Wold Gustafson</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.54,89</t>
+          <t>2.54,30</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -13064,12 +13169,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Ane Viken Refseth</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2.54,81</t>
+          <t>2.54,89</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -13077,7 +13182,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -13099,25 +13204,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.54,95</t>
+          <t>2.54,81</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>09.05.2010</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -13134,12 +13239,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Dorottya Csejtey</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.55,05</t>
+          <t>2.54,95</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -13147,12 +13252,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>12.02.2017</t>
+          <t>09.05.2010</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -13169,25 +13274,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Helene Marie Haram</t>
+          <t>Dorottya Csejtey</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2.55,46</t>
+          <t>2.55,05</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>12.02.2017</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -13204,25 +13309,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Helene Marie Haram</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2.56,00</t>
+          <t>2.55,46</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -13239,25 +13344,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mari Helen Hammer</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2.57,09</t>
+          <t>2.56,00</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>24.06.2007</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -13274,25 +13379,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Mari Helen Hammer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2.57,44</t>
+          <t>2.57,09</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20.03.2022</t>
+          <t>24.06.2007</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -13309,25 +13414,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.57,65</t>
+          <t>2.57,44</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>20.03.2022</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -13344,20 +13449,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.57,86</t>
+          <t>2.57,65</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -13379,25 +13484,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2.58,22</t>
+          <t>2.57,86</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -13414,25 +13519,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2.58,42</t>
+          <t>2.58,22</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -13449,25 +13554,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Olivia Sterud Prytz</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3.00,16</t>
+          <t>2.59,53</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10.11.2019</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -13484,25 +13589,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Sofie Hepsø</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3.00,30</t>
+          <t>2.59,83</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>05.09.2021</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -13519,25 +13624,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Olivia Sterud Prytz</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3.00,36</t>
+          <t>3.00,16</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>10.11.2019</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -13554,20 +13659,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Julie Wiik Arnesen</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3.01,41</t>
+          <t>3.00,30</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>05.09.2021</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -13589,25 +13694,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3.01,59</t>
+          <t>3.00,36</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -13624,25 +13729,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Izabele Farias Ribeiro</t>
+          <t>Kristina Aleman Sandsund</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.01,60</t>
+          <t>3.00,85</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -13659,25 +13764,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Julie Wiik Arnesen</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3.01,78</t>
+          <t>3.01,41</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>09.02.2019</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -13694,25 +13799,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3.01,70</t>
+          <t>3.01,59</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -13729,25 +13834,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tone Killingberg</t>
+          <t>Izabele Farias Ribeiro</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3.02,21</t>
+          <t>3.01,60</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>18.06.2016</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -13764,20 +13869,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Silje Dahle</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3.02,65</t>
+          <t>3.01,78</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>07.02.2016</t>
+          <t>09.02.2019</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -13799,20 +13904,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Emilie Ying Ulstad Hovland</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3.03,25</t>
+          <t>3.01,58</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>29.03.2025</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -13834,25 +13939,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Anna Svendsen</t>
+          <t>Tone Killingberg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3.03,27</t>
+          <t>3.02,21</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>18.06.2016</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -13869,25 +13974,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Aase Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.04,07</t>
+          <t>3.02,65</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>07.02.2016</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -13904,25 +14009,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Elisabeth Holm</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3.04,88</t>
+          <t>3.02,91</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12.03.2005</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -13939,25 +14044,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sofie Hepsø</t>
+          <t>Emilie Ying Ulstad Hovland</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.05,47</t>
+          <t>3.03,25</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>29.03.2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -13974,25 +14079,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Anna Svendsen</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3.05,49</t>
+          <t>3.03,27</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>13.02.2022</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -14009,25 +14114,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ola vatn Gundersen</t>
+          <t>Elisabeth Holm</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2.46,87</t>
+          <t>3.04,88</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>11.02.2018</t>
+          <t>12.03.2005</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -14044,25 +14149,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sunniva Belsnes</t>
+          <t>Ola vatn Gundersen</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3.05,98</t>
+          <t>2.46,87</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>21.04.2018</t>
+          <t>11.02.2018</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -14079,25 +14184,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sara Skaalvik Trelstad</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3.07,55</t>
+          <t>3.05,49</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>05.04.2014</t>
+          <t>13.02.2022</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -14114,25 +14219,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Maria Bøe</t>
+          <t>Sunniva Belsnes</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.07,59</t>
+          <t>3.05,98</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>24.05.2009</t>
+          <t>21.04.2018</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -14154,20 +14259,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3.07,64</t>
+          <t>3.06,39</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -14184,25 +14289,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hansine Rindberg Monsø</t>
+          <t>Maria Bøe</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3.07,67</t>
+          <t>3.07,59</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>24.05.2009</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -14219,25 +14324,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Sara Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3.07,93</t>
+          <t>3.07,55</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>05.04.2014</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -14254,20 +14359,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3.07,90</t>
+          <t>3.07,49</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -14289,25 +14394,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Line Steine Bertelsen</t>
+          <t>Hansine Rindberg Monsø</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3.08,74</t>
+          <t>3.07,67</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>16.02.2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -14324,25 +14429,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3.09,44</t>
+          <t>3.07,90</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -14359,20 +14464,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Elisaveta Røste</t>
+          <t>Line Steine Bertelsen</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.10,87</t>
+          <t>3.08,74</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>19.06.2021</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -14394,25 +14499,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2.54,08</t>
+          <t>3.09,44</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20.04.2013</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -14429,25 +14534,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Michaela Josefin Abeleva Barrera</t>
+          <t>Elisaveta Røste</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3.13,74</t>
+          <t>3.10,87</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -14464,20 +14569,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sofia Bjørklund Mora</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.14,90</t>
+          <t>2.54,08</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>20.04.2013</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -14499,25 +14604,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Elise Øystrøm Tyvold</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3.16,51</t>
+          <t>3.14,18</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>30.09.2019</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -14534,25 +14639,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Sofia Bjørklund Mora</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.16,96</t>
+          <t>3.14,90</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -14569,25 +14674,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Elise Øystrøm Tyvold</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2.57,64</t>
+          <t>3.16,51</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>14.09.2024</t>
+          <t>30.09.2019</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -14604,25 +14709,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.17,22</t>
+          <t>3.16,96</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14639,20 +14744,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Helle Lundgren</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.18,05</t>
+          <t>2.57,64</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>14.09.2024</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -14674,12 +14779,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Helle Lundgren</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.18,09</t>
+          <t>3.18,05</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -14687,7 +14792,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>15.06.2013</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -14709,20 +14814,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.18,96</t>
+          <t>3.18,09</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>16.01.2005</t>
+          <t>15.06.2013</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -14744,25 +14849,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3.19,51</t>
+          <t>3.18,96</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>16.01.2005</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14779,20 +14884,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.19,94</t>
+          <t>3.19,11</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -14814,25 +14919,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sigrid Moen Henriksen</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3.21,97</t>
+          <t>3.19,51</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14849,25 +14954,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ingrid Lianes</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.22,34</t>
+          <t>3.19,94</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>24.05.2009</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14884,20 +14989,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Marte Hemmer</t>
+          <t>Sigrid Moen Henriksen</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3.24,21</t>
+          <t>3.21,97</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>16.01.2005</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -14919,25 +15024,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Amalie Solvoll</t>
+          <t>Ingrid Lianes</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.24,06</t>
+          <t>3.22,34</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>17.03.2019</t>
+          <t>24.05.2009</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -14954,25 +15059,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Pia Helena Wildhagen</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3.24,94</t>
+          <t>3.23,19</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>01.10.2017</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14989,25 +15094,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Aurora S. Juel</t>
+          <t>Amalie Solvoll</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3.25,84</t>
+          <t>3.24,06</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>17.03.2019</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -15024,25 +15129,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Madeleine Tran Wæraas</t>
+          <t>Marte Hemmer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3.25,81</t>
+          <t>3.24,21</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>27.10.2019</t>
+          <t>16.01.2005</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -15059,25 +15164,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Amalie Gylseth Dahl</t>
+          <t>Pia Helena Wildhagen</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3.30,05</t>
+          <t>3.24,94</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>01.10.2017</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -15094,20 +15199,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Luma Nicole Farias Kristiansen</t>
+          <t>Aurora S. Juel</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.30,73</t>
+          <t>3.25,84</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -15129,25 +15234,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Emma Nedeea Hagen</t>
+          <t>Madeleine Tran Wæraas</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3.32,61</t>
+          <t>3.25,81</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>30.04.2022</t>
+          <t>27.10.2019</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -15164,25 +15269,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cathrine Hegle</t>
+          <t>Amalie Gylseth Dahl</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.32,39</t>
+          <t>3.30,05</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>04.12.2010</t>
+          <t>12.11.2023</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -15199,25 +15304,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mia Bretun Finserå</t>
+          <t>Luma Nicole Farias Kristiansen</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3.34,01</t>
+          <t>3.30,73</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>28.10.2012</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -15234,25 +15339,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Emma Nedeea Hagen</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.37,34</t>
+          <t>3.32,61</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>30.04.2022</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -15269,25 +15374,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Cathrine Hegle</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3.38,35</t>
+          <t>3.32,39</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>04.12.2010</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -15304,25 +15409,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Julia Tan</t>
+          <t>Hedda Gätzschmann</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.39,62</t>
+          <t>3.31,95</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>19.04.2009</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -15339,25 +15444,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Victoria Dessen</t>
+          <t>Mia Bretun Finserå</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3.39,66</t>
+          <t>3.34,01</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>12.03.2005</t>
+          <t>28.10.2012</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -15374,25 +15479,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Emilie Sandvik Gangåssæter</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3.41,36</t>
+          <t>3.34,44</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>28.09.2019</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -15409,20 +15514,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3.45,09</t>
+          <t>3.35,59</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15444,25 +15549,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ingrid Skye Naustvoll</t>
+          <t>Julia Tan</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3.45,61</t>
+          <t>3.39,62</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>23.11.2013</t>
+          <t>19.04.2009</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -15479,25 +15584,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lea almaas</t>
+          <t>Victoria Dessen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3.45,63</t>
+          <t>3.39,66</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>21.01.2012</t>
+          <t>12.03.2005</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -15514,25 +15619,25 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Emilie Sandvik Gangåssæter</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3.49,47</t>
+          <t>3.41,36</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>28.09.2019</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -15549,25 +15654,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ronja Emilia Wikström</t>
+          <t>Ilaria Kari Cherubini</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3.50,23</t>
+          <t>3.43,26</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -15584,25 +15689,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Frida Merethe Norli Eidsvåg</t>
+          <t>Nicoline Vinje</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3.55,06</t>
+          <t>3.43,38</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -15619,25 +15724,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Lena Sofie Hammer</t>
+          <t>Ingrid Skye Naustvoll</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3.56,82</t>
+          <t>3.45,61</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>23.11.2013</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -15654,25 +15759,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Julia Beatrice Ferreira Kristiansen</t>
+          <t>Lea almaas</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3.56,98</t>
+          <t>3.45,63</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>04.12.2016</t>
+          <t>21.01.2012</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -15689,25 +15794,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Aida Smalø Moen</t>
+          <t>Live Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3.58,71</t>
+          <t>3.46,43</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>21.01.2012</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -15724,20 +15829,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Nicoline Vinje</t>
+          <t>Sigrid Gylseth Dahl</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4.02,93</t>
+          <t>3.47,69</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -15759,25 +15864,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Karoline Skjevik</t>
+          <t>Ronja Emilia Wikström</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4.02,48</t>
+          <t>3.50,23</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>23.02.2008</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -15794,20 +15899,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Marita Fuglestad Løkken</t>
+          <t>Frida Merethe Norli Eidsvåg</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4.04,01</t>
+          <t>3.55,06</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>15.06.2013</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -15829,20 +15934,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ramona Vutudal</t>
+          <t>Lena Sofie Hammer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4.05,46</t>
+          <t>3.56,82</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>25.01.2009</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -15864,25 +15969,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Julia Beatrice Ferreira Kristiansen</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4.05,94</t>
+          <t>3.56,98</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>04.12.2016</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -15899,25 +16004,25 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Anna Fenstad Høysæter</t>
+          <t>Aida Smalø Moen</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4.13,87</t>
+          <t>3.58,71</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>21.01.2012</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -15934,25 +16039,25 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Live Hamnes Ulriksen</t>
+          <t>Karoline Skjevik</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>4.14,34</t>
+          <t>4.02,48</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>23.02.2008</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -15969,25 +16074,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Charlotte Talseth</t>
+          <t>Marita Fuglestad Løkken</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>4.17,14</t>
+          <t>4.04,01</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>15.06.2013</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -16004,20 +16109,20 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Olivia Hjelmeseth Larsen</t>
+          <t>Ramona Vutudal</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4.20,30</t>
+          <t>4.05,46</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>30.04.2022</t>
+          <t>25.01.2009</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -16039,25 +16144,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Julie Gilbu</t>
+          <t>Sara Olea  Riseth Moe</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>4.21,16</t>
+          <t>4.07,04</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>14.03.2015</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -16074,25 +16179,25 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Hedda Larsen Natvig</t>
+          <t>Anna Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4.22,93</t>
+          <t>4.13,87</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -16109,20 +16214,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Amelia Roaldseth</t>
+          <t>Charlotte Talseth</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4.25,63</t>
+          <t>4.17,14</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>19.04.2008</t>
+          <t>22.02.2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -16144,25 +16249,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Connie Rakel Lånke</t>
+          <t>Olivia Hjelmeseth Larsen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>4.31,30</t>
+          <t>4.20,30</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>05.04.2014</t>
+          <t>30.04.2022</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -16179,25 +16284,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sunniva Eldholm</t>
+          <t>Julie Gilbu</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>4.35,46</t>
+          <t>4.21,16</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>17.04.2021</t>
+          <t>14.03.2015</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -16214,25 +16319,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Camilla Gervasoni</t>
+          <t>Hedda Larsen Natvig</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>4.39,35</t>
+          <t>4.22,93</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -16249,20 +16354,20 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Kristine Haram Bye</t>
+          <t>Amelia Roaldseth</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>4.43,86</t>
+          <t>4.25,63</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>04.12.2010</t>
+          <t>19.04.2008</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -16284,33 +16389,173 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>Connie Rakel Lånke</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4.31,30</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>90</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>05.04.2014</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sunniva Eldholm</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4.35,46</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>86</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>17.04.2021</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Camilla Gervasoni</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>4.39,35</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>83</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>03.12.2011</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Kristine Haram Bye</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>4.43,86</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>79</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>04.12.2010</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
           <t>Phoebe Thalberg Fagerheim</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>5.02,97</t>
         </is>
       </c>
-      <c r="C174" t="n">
+      <c r="C178" t="n">
         <v>65</v>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>09.10.2011</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>Trondheim</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -17070,12 +17315,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Edle Lund</t>
+          <t>Solveig Natvig Løvseth</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.50,56</t>
+          <t>2.50,50</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -17083,12 +17328,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>09.06.2017</t>
+          <t>03.05.2014</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Drammen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -17105,12 +17350,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solveig Natvig Løvseth</t>
+          <t>Edle Lund</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.50,50</t>
+          <t>2.50,56</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -17118,12 +17363,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>03.05.2014</t>
+          <t>09.06.2017</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Drammen</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -17805,12 +18050,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.57,81</t>
+          <t>2.40,77</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -17818,7 +18063,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30.04.2022</t>
+          <t>13.06.2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -17840,12 +18085,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.40,77</t>
+          <t>2.57,81</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -17853,7 +18098,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13.06.2025</t>
+          <t>30.04.2022</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -18820,12 +19065,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3.22,31</t>
+          <t>3.22,16</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -18833,12 +19078,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>05.06.2021</t>
+          <t>12.06.2009</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -18855,12 +19100,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3.22,16</t>
+          <t>3.22,31</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -18868,12 +19113,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12.06.2009</t>
+          <t>05.06.2021</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -19100,12 +19345,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Kirsti Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3.35,10</t>
+          <t>3.35,21</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -19113,7 +19358,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>13.06.2025</t>
+          <t>12.06.2015</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -19135,12 +19380,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kirsti Bjørnsdatter Paulsen</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3.35,21</t>
+          <t>3.35,10</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -19148,7 +19393,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12.06.2015</t>
+          <t>13.06.2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
